--- a/artfynd/A 50817-2025 artfynd.xlsx
+++ b/artfynd/A 50817-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2149,6 +2149,321 @@
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>129505731</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Västra Kolgården, Mpd</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>589615</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6932954</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>129505874</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Västra kolgården, Mpd</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>589400</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6932928</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>129503437</v>
+      </c>
+      <c r="B17" t="n">
+        <v>98716</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Västra kolgården, Mpd</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>589382</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6932944</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 50817-2025 artfynd.xlsx
+++ b/artfynd/A 50817-2025 artfynd.xlsx
@@ -2368,7 +2368,7 @@
         <v>129503437</v>
       </c>
       <c r="B17" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 50817-2025 artfynd.xlsx
+++ b/artfynd/A 50817-2025 artfynd.xlsx
@@ -2368,7 +2368,7 @@
         <v>129503437</v>
       </c>
       <c r="B17" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 50817-2025 artfynd.xlsx
+++ b/artfynd/A 50817-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2464,6 +2464,103 @@
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>129505777</v>
+      </c>
+      <c r="B18" t="n">
+        <v>92203</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>1339</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Brandticka</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Pycnoporellus fulgens</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Talltita, Västra Kolgården  Sättna, Mpd</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>589570</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6932942</v>
+      </c>
+      <c r="S18" t="n">
+        <v>25</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 50817-2025 artfynd.xlsx
+++ b/artfynd/A 50817-2025 artfynd.xlsx
@@ -2154,7 +2154,7 @@
         <v>129505731</v>
       </c>
       <c r="B15" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2261,7 +2261,7 @@
         <v>129505874</v>
       </c>
       <c r="B16" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
         <v>129503437</v>
       </c>
       <c r="B17" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2469,7 +2469,7 @@
         <v>129505777</v>
       </c>
       <c r="B18" t="n">
-        <v>92203</v>
+        <v>92231</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 50817-2025 artfynd.xlsx
+++ b/artfynd/A 50817-2025 artfynd.xlsx
@@ -2154,7 +2154,7 @@
         <v>129505731</v>
       </c>
       <c r="B15" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2261,7 +2261,7 @@
         <v>129505874</v>
       </c>
       <c r="B16" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
         <v>129503437</v>
       </c>
       <c r="B17" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2469,7 +2469,7 @@
         <v>129505777</v>
       </c>
       <c r="B18" t="n">
-        <v>92231</v>
+        <v>92237</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 50817-2025 artfynd.xlsx
+++ b/artfynd/A 50817-2025 artfynd.xlsx
@@ -2151,50 +2151,49 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129505731</v>
+        <v>129503437</v>
       </c>
       <c r="B15" t="n">
-        <v>57735</v>
+        <v>98769</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>25</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Västra Kolgården, Mpd</t>
+          <t>Västra kolgården, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>589615</v>
+        <v>589382</v>
       </c>
       <c r="R15" t="n">
-        <v>6932954</v>
+        <v>6932944</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2227,11 +2226,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-11-03</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2258,53 +2252,48 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129505874</v>
+        <v>129505777</v>
       </c>
       <c r="B16" t="n">
-        <v>57735</v>
+        <v>92238</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>1339</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Västra kolgården, Mpd</t>
+          <t>Talltita, Västra Kolgården  Sättna, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>589400</v>
+        <v>589570</v>
       </c>
       <c r="R16" t="n">
-        <v>6932928</v>
+        <v>6932942</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2334,11 +2323,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-11-03</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2365,49 +2349,50 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129503437</v>
+        <v>129505731</v>
       </c>
       <c r="B17" t="n">
-        <v>98768</v>
+        <v>57736</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>25</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Västra kolgården, Mpd</t>
+          <t>Västra Kolgården, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>589382</v>
+        <v>589615</v>
       </c>
       <c r="R17" t="n">
-        <v>6932944</v>
+        <v>6932954</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2440,6 +2425,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2466,48 +2456,53 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129505777</v>
+        <v>129505874</v>
       </c>
       <c r="B18" t="n">
-        <v>92237</v>
+        <v>57736</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1339</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Talltita, Västra Kolgården  Sättna, Mpd</t>
+          <t>Västra kolgården, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>589570</v>
+        <v>589400</v>
       </c>
       <c r="R18" t="n">
-        <v>6932942</v>
+        <v>6932928</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2537,6 +2532,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 50817-2025 artfynd.xlsx
+++ b/artfynd/A 50817-2025 artfynd.xlsx
@@ -2154,7 +2154,7 @@
         <v>129503437</v>
       </c>
       <c r="B15" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2255,7 +2255,7 @@
         <v>129505777</v>
       </c>
       <c r="B16" t="n">
-        <v>92238</v>
+        <v>92243</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 50817-2025 artfynd.xlsx
+++ b/artfynd/A 50817-2025 artfynd.xlsx
@@ -2154,7 +2154,7 @@
         <v>129503437</v>
       </c>
       <c r="B15" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2255,7 +2255,7 @@
         <v>129505777</v>
       </c>
       <c r="B16" t="n">
-        <v>92243</v>
+        <v>92247</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 50817-2025 artfynd.xlsx
+++ b/artfynd/A 50817-2025 artfynd.xlsx
@@ -2154,7 +2154,7 @@
         <v>129503437</v>
       </c>
       <c r="B15" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2255,7 +2255,7 @@
         <v>129505777</v>
       </c>
       <c r="B16" t="n">
-        <v>92247</v>
+        <v>92249</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 50817-2025 artfynd.xlsx
+++ b/artfynd/A 50817-2025 artfynd.xlsx
@@ -2154,7 +2154,7 @@
         <v>129503437</v>
       </c>
       <c r="B15" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 50817-2025 artfynd.xlsx
+++ b/artfynd/A 50817-2025 artfynd.xlsx
@@ -2352,7 +2352,7 @@
         <v>129505731</v>
       </c>
       <c r="B17" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2459,7 +2459,7 @@
         <v>129505874</v>
       </c>
       <c r="B18" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 50817-2025 artfynd.xlsx
+++ b/artfynd/A 50817-2025 artfynd.xlsx
@@ -2255,7 +2255,7 @@
         <v>129505777</v>
       </c>
       <c r="B16" t="n">
-        <v>92249</v>
+        <v>92252</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 50817-2025 artfynd.xlsx
+++ b/artfynd/A 50817-2025 artfynd.xlsx
@@ -2566,7 +2566,7 @@
         <v>129852821</v>
       </c>
       <c r="B19" t="n">
-        <v>99130</v>
+        <v>99133</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 50817-2025 artfynd.xlsx
+++ b/artfynd/A 50817-2025 artfynd.xlsx
@@ -2566,7 +2566,7 @@
         <v>129852821</v>
       </c>
       <c r="B19" t="n">
-        <v>99133</v>
+        <v>99141</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 50817-2025 artfynd.xlsx
+++ b/artfynd/A 50817-2025 artfynd.xlsx
@@ -2566,7 +2566,7 @@
         <v>129852821</v>
       </c>
       <c r="B19" t="n">
-        <v>99141</v>
+        <v>99151</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 50817-2025 artfynd.xlsx
+++ b/artfynd/A 50817-2025 artfynd.xlsx
@@ -2566,7 +2566,7 @@
         <v>129852821</v>
       </c>
       <c r="B19" t="n">
-        <v>99151</v>
+        <v>99152</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 50817-2025 artfynd.xlsx
+++ b/artfynd/A 50817-2025 artfynd.xlsx
@@ -2566,7 +2566,7 @@
         <v>129852821</v>
       </c>
       <c r="B19" t="n">
-        <v>99152</v>
+        <v>99153</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 50817-2025 artfynd.xlsx
+++ b/artfynd/A 50817-2025 artfynd.xlsx
@@ -2566,7 +2566,7 @@
         <v>129852821</v>
       </c>
       <c r="B19" t="n">
-        <v>99153</v>
+        <v>99154</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 50817-2025 artfynd.xlsx
+++ b/artfynd/A 50817-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AY32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124074060</v>
+        <v>124068927</v>
       </c>
       <c r="B2" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Garnlav, Mpd</t>
+          <t>Ullticka, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>589544</v>
+        <v>589743</v>
       </c>
       <c r="R2" t="n">
-        <v>6933095</v>
+        <v>6932931</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -765,60 +760,47 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124067954</v>
+        <v>129505777</v>
       </c>
       <c r="B3" t="n">
-        <v>57666</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92564</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>1339</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Talltita, Västra Kolgården  Sättna, Mpd</t>
@@ -855,17 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Lyckades inte fånga dom på video men ljudet fick jag med i alla fall.</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,50 +869,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124069676</v>
+        <v>124072091</v>
       </c>
       <c r="B4" t="n">
-        <v>56722</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Spillning tjäder , Mpd</t>
+          <t>Garnlav , Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>589496</v>
+        <v>589601</v>
       </c>
       <c r="R4" t="n">
-        <v>6932984</v>
+        <v>6933092</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -967,7 +939,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -977,7 +949,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1004,50 +976,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124074129</v>
+        <v>124074060</v>
       </c>
       <c r="B5" t="n">
-        <v>56722</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Tjäder spillning , Mpd</t>
+          <t>Garnlav, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>589507</v>
+        <v>589544</v>
       </c>
       <c r="R5" t="n">
-        <v>6933042</v>
+        <v>6933095</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1077,19 +1044,9 @@
           <t>2025-04-14</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>16:53</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-04-14</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>16:53</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1116,50 +1073,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124069769</v>
+        <v>124068567</v>
       </c>
       <c r="B6" t="n">
-        <v>43834</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>101735</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Jättesvampmal , Mpd</t>
+          <t>Gullticka, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>589492</v>
+        <v>589404</v>
       </c>
       <c r="R6" t="n">
-        <v>6932983</v>
+        <v>6932990</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1191,7 +1143,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1201,7 +1153,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1231,12 +1183,7 @@
         <v>124070322</v>
       </c>
       <c r="B7" t="n">
-        <v>79891</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1340,55 +1287,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124071023</v>
+        <v>124071156</v>
       </c>
       <c r="B8" t="n">
-        <v>56722</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Spillning tjäder, Mpd</t>
+          <t>Lunglav , Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>589645</v>
+        <v>589686</v>
       </c>
       <c r="R8" t="n">
-        <v>6933017</v>
+        <v>6933010</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1420,7 +1357,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1430,12 +1367,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:53</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>2 honor 1 hane på platts. Skrämdes iväg</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1462,46 +1394,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124072716</v>
+        <v>124073240</v>
       </c>
       <c r="B9" t="n">
-        <v>98021</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>223597</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Jungfru Marie nycklar , Mpd</t>
+          <t>Lunglav , Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>589428</v>
+        <v>589521</v>
       </c>
       <c r="R9" t="n">
-        <v>6933039</v>
+        <v>6933138</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1533,7 +1464,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1543,7 +1474,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1570,50 +1501,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124074305</v>
+        <v>124735185</v>
       </c>
       <c r="B10" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Knärot, Mpd</t>
+          <t>Näverbäcken , Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>589450</v>
+        <v>589665</v>
       </c>
       <c r="R10" t="n">
-        <v>6933023</v>
+        <v>6933025</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1640,22 +1566,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1682,15 +1608,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124068567</v>
+        <v>124740983</v>
       </c>
       <c r="B11" t="n">
-        <v>79891</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1718,14 +1639,14 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Gullticka, Mpd</t>
+          <t>Näverbäcken , Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>589404</v>
+        <v>589413</v>
       </c>
       <c r="R11" t="n">
-        <v>6932990</v>
+        <v>6932907</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1752,22 +1673,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1794,46 +1715,50 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124070434</v>
+        <v>129505689</v>
       </c>
       <c r="B12" t="n">
-        <v>98021</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>223597</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Jungfru Marie nycklar , Mpd</t>
+          <t>Västra Kolgården, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>589589</v>
+        <v>589699</v>
       </c>
       <c r="R12" t="n">
-        <v>6932987</v>
+        <v>6932982</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1860,22 +1785,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>14:11</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>14:11</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1890,77 +1805,62 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124069531</v>
+        <v>129505731</v>
       </c>
       <c r="B13" t="n">
-        <v>56722</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Tjäder, Mpd</t>
+          <t>Västra Kolgården, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>589493</v>
+        <v>589615</v>
       </c>
       <c r="R13" t="n">
-        <v>6932974</v>
+        <v>6932954</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1987,27 +1887,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>13:36</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>13:36</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Skrämde upp den bakom en låga. Hona.</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2022,67 +1912,62 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124737718</v>
+        <v>129505874</v>
       </c>
       <c r="B14" t="n">
-        <v>56836</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Näverbäcken , Mpd</t>
+          <t>Västra kolgården, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>589627</v>
+        <v>589400</v>
       </c>
       <c r="R14" t="n">
-        <v>6933029</v>
+        <v>6932928</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2109,22 +1994,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>10:38</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>10:38</t>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2139,61 +2019,72 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129503437</v>
+        <v>124069531</v>
       </c>
       <c r="B15" t="n">
-        <v>98790</v>
+        <v>57141</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>25</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Västra kolgården, Mpd</t>
+          <t>Tjäder, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>589382</v>
+        <v>589493</v>
       </c>
       <c r="R15" t="n">
-        <v>6932944</v>
+        <v>6932974</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2220,12 +2111,27 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Skrämde upp den bakom en låga. Hona.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2240,22 +2146,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129505777</v>
+        <v>124069676</v>
       </c>
       <c r="B16" t="n">
-        <v>92255</v>
+        <v>57141</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2263,37 +2169,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1339</v>
+        <v>100138</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Talltita, Västra Kolgården  Sättna, Mpd</t>
+          <t>Spillning tjäder , Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>589570</v>
+        <v>589496</v>
       </c>
       <c r="R16" t="n">
-        <v>6932942</v>
+        <v>6932984</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2317,12 +2223,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2337,62 +2253,62 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129505731</v>
+        <v>124071023</v>
       </c>
       <c r="B17" t="n">
-        <v>57741</v>
+        <v>57141</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Västra Kolgården, Mpd</t>
+          <t>Spillning tjäder, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>589615</v>
+        <v>589645</v>
       </c>
       <c r="R17" t="n">
-        <v>6932954</v>
+        <v>6933017</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2419,17 +2335,27 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>2 honor 1 hane på platts. Skrämdes iväg</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2444,62 +2370,57 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129505874</v>
+        <v>124071833</v>
       </c>
       <c r="B18" t="n">
-        <v>57741</v>
+        <v>57141</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Västra kolgården, Mpd</t>
+          <t>Spillning tjäder, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>589400</v>
+        <v>589653</v>
       </c>
       <c r="R18" t="n">
-        <v>6932928</v>
+        <v>6933043</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2526,17 +2447,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2551,22 +2477,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129852821</v>
+        <v>124074129</v>
       </c>
       <c r="B19" t="n">
-        <v>99157</v>
+        <v>57141</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2574,34 +2500,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>219874</v>
+        <v>100138</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Högsvedjan, Mpd</t>
+          <t>Tjäder spillning , Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>589463</v>
+        <v>589507</v>
       </c>
       <c r="R19" t="n">
-        <v>6933048</v>
+        <v>6933042</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2628,12 +2554,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2648,15 +2584,1400 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>124737718</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Näverbäcken , Mpd</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>589627</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6933029</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>10:38</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>10:38</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>124069769</v>
+      </c>
+      <c r="B21" t="n">
+        <v>44177</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>101735</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Jättesvampmal</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Scardia boletella</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Fabricius, 1794)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Jättesvampmal , Mpd</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>589492</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6932983</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>13:47</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>13:47</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>124067133</v>
+      </c>
+      <c r="B22" t="n">
+        <v>57132</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Järpe Spillning , Mpd</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>589368</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6932909</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Måtten och innehållet överensstämmer med järpens spillning.</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>124068269</v>
+      </c>
+      <c r="B23" t="n">
+        <v>57132</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Järpe, Mpd</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>589512</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6932934</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Spillning</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Dropping</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>124068463</v>
+      </c>
+      <c r="B24" t="n">
+        <v>57144</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>102613</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Orre</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Lyrurus tetrix</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Orre, Mpd</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>589559</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6932909</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>124067954</v>
+      </c>
+      <c r="B25" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Talltita, Västra Kolgården  Sättna, Mpd</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>589570</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6932942</v>
+      </c>
+      <c r="S25" t="n">
+        <v>25</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Lyckades inte fånga dom på video men ljudet fick jag med i alla fall.</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>129503676</v>
+      </c>
+      <c r="B26" t="n">
+        <v>58057</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Västra Kolgården, Mpd</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>589566</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6932896</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Fick dålig video på dem, men jag såg klart och tydligt att det var lavskrikor.</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>129852821</v>
+      </c>
+      <c r="B27" t="n">
+        <v>99230</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>219874</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Nattviol</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Högsvedjan, Mpd</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>589463</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6933048</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
           <t>Tim Nordvall</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
+      <c r="AX27" t="inlineStr">
         <is>
           <t>Tim Nordvall</t>
         </is>
       </c>
-      <c r="AY19" t="inlineStr"/>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>124074305</v>
+      </c>
+      <c r="B28" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Knärot, Mpd</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>589450</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6933023</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>17:01</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>17:01</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>129503437</v>
+      </c>
+      <c r="B29" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Västra kolgården, Mpd</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>589382</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6932944</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>129505836</v>
+      </c>
+      <c r="B30" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Västra Kolgården, Mpd</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>589494</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6932939</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>124070434</v>
+      </c>
+      <c r="B31" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Jungfru Marie nycklar , Mpd</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>589589</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6932987</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>124067852</v>
+      </c>
+      <c r="B32" t="n">
+        <v>79328</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>230405</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Garnlav (ssp. sarmentosa)</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Järpe Spillning , Mpd</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>589368</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6932909</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>12:33</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>12:33</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ingen mittensträng, går av lätt.</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 50817-2025 artfynd.xlsx
+++ b/artfynd/A 50817-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY32"/>
+  <dimension ref="A1:AZ32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129505777</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124072091</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -973,6 +988,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124074060</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,6 +1100,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124068567</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1187,6 +1212,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124070322</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1294,6 +1324,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124073240</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1401,6 +1436,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124740983</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1508,6 +1548,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129505731</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1615,6 +1660,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129505874</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1742,6 +1792,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124069531</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1849,6 +1904,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124069676</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1966,6 +2026,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124071023</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2073,6 +2138,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124074129</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2185,6 +2255,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124737718</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2292,6 +2367,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124069769</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2404,6 +2484,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124067133</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2511,6 +2596,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124068269</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2613,6 +2703,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124068463</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2723,6 +2818,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124067954</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2837,6 +2937,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129503676</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2934,6 +3039,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129852821</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3041,6 +3151,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124074305</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3142,6 +3257,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129503437</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3243,6 +3363,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129505836</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3346,6 +3471,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124070434</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3458,6 +3588,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124067852</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3555,6 +3690,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124068927</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3662,6 +3802,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124071156</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3769,6 +3914,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124735185</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3871,6 +4021,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129505689</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3978,8 +4133,46 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124071833</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>